--- a/Assets/Scripts/HH/Quest/QuestTable.xlsx
+++ b/Assets/Scripts/HH/Quest/QuestTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\HH\Quest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F190524-D362-474E-8533-10C3C19E4EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145B48A2-CCF2-455E-B8DB-29D53CFBB301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D7B09D39-F076-47B8-9C94-38323AFFEA98}"/>
   </bookViews>
@@ -36,88 +36,582 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>Food</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>questName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>questItemType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>questInfo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>reward</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>questText</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buyOrSell</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>villageType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>questType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Trade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>questStuffName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="190">
   <si>
     <t>Smokian</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Smokian</t>
+  </si>
+  <si>
+    <t>questName</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>questStuffName</t>
+  </si>
+  <si>
+    <t>questInfo</t>
+  </si>
+  <si>
+    <t>reward</t>
+  </si>
+  <si>
+    <t>questText</t>
+  </si>
+  <si>
+    <t>buyOrSell</t>
+  </si>
+  <si>
+    <t>villageType</t>
+  </si>
+  <si>
+    <t>questType</t>
+  </si>
+  <si>
+    <t>Wheat1</t>
+  </si>
+  <si>
+    <t>Food buy 30kg(GreStar)</t>
+  </si>
+  <si>
+    <t>GreStar</t>
+  </si>
+  <si>
+    <t>Trade</t>
+  </si>
+  <si>
+    <t>Wheat2</t>
+  </si>
+  <si>
+    <t>Food Delivery</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>Wheat3</t>
+  </si>
+  <si>
+    <t>Food buy 80kg</t>
+  </si>
+  <si>
+    <t>Barley1</t>
+  </si>
+  <si>
+    <t>Barley2</t>
+  </si>
+  <si>
+    <t>Food buy 30kg</t>
+  </si>
+  <si>
     <t>GoldBen</t>
+  </si>
+  <si>
+    <t>Barley3</t>
+  </si>
+  <si>
+    <t>Oats1</t>
+  </si>
+  <si>
+    <t>Food buy 20kg</t>
+  </si>
+  <si>
+    <t>Oats2</t>
+  </si>
+  <si>
+    <t>Oats3</t>
+  </si>
+  <si>
+    <t>Food buy 70kg</t>
+  </si>
+  <si>
+    <t>Fish1</t>
+  </si>
+  <si>
+    <t>Fish2</t>
+  </si>
+  <si>
+    <t>Food buy 50kg</t>
+  </si>
+  <si>
+    <t>Fish3</t>
+  </si>
+  <si>
+    <t>Meat1</t>
+  </si>
+  <si>
+    <t>Meat2</t>
+  </si>
+  <si>
+    <t>Meat3</t>
+  </si>
+  <si>
+    <t>Food buy 100kg</t>
+  </si>
+  <si>
+    <t>Apple1</t>
+  </si>
+  <si>
+    <t>Apple2</t>
+  </si>
+  <si>
+    <t>Food buy 40kg</t>
+  </si>
+  <si>
+    <t>Apple3</t>
+  </si>
+  <si>
+    <t>Grape1</t>
+  </si>
+  <si>
+    <t>Food buy 10kg</t>
+  </si>
+  <si>
+    <t>Grape2</t>
+  </si>
+  <si>
+    <t>Grape3</t>
+  </si>
+  <si>
+    <t>Bread1</t>
+  </si>
+  <si>
+    <t>ProcessedFood Delivery</t>
+  </si>
+  <si>
+    <t>Bread2</t>
+  </si>
+  <si>
+    <t>ProcessedFood buy 40kg</t>
+  </si>
+  <si>
+    <t>Bread3</t>
+  </si>
+  <si>
+    <t>SmokedFish1</t>
+  </si>
+  <si>
+    <t>ProcessedFood buy 30kg</t>
+  </si>
+  <si>
+    <t>SmokedFish2</t>
+  </si>
+  <si>
+    <t>SmokedFish3</t>
+  </si>
+  <si>
+    <t>ProcessedFood buy 70kg</t>
+  </si>
+  <si>
+    <t>SmokedMeat1</t>
+  </si>
+  <si>
+    <t>SmokedMeat2</t>
+  </si>
+  <si>
+    <t>ProcessedFood buy 60kg</t>
+  </si>
+  <si>
+    <t>SmokdeMeat3</t>
+  </si>
+  <si>
+    <t>AppleWine1</t>
+  </si>
+  <si>
+    <t>ProcessedFood buy 3kg</t>
+  </si>
+  <si>
+    <t>AppleWine2</t>
+  </si>
+  <si>
+    <t>AppleWine3</t>
+  </si>
+  <si>
+    <t>ProcessedFood buy 12kg</t>
+  </si>
+  <si>
+    <t>GrapeWine1</t>
+  </si>
+  <si>
+    <t>GrapeWine2</t>
+  </si>
+  <si>
+    <t>ProcessedFood buy 6kg</t>
+  </si>
+  <si>
+    <t>GrapeWine3</t>
+  </si>
+  <si>
+    <t>Fruitjam1</t>
+  </si>
+  <si>
+    <t>Fruitjam2</t>
+  </si>
+  <si>
+    <t>Fruitjam3</t>
+  </si>
+  <si>
+    <t>ProcessedFood buy 13kg</t>
+  </si>
+  <si>
+    <t>Dress1</t>
+  </si>
+  <si>
+    <t>Clothing Delivery</t>
+  </si>
+  <si>
+    <t>Dress2</t>
+  </si>
+  <si>
+    <t>Clothing buy 7</t>
+  </si>
+  <si>
+    <t>Dress3</t>
+  </si>
+  <si>
+    <t>Suit1</t>
+  </si>
+  <si>
+    <t>Clothing buy 2</t>
+  </si>
+  <si>
+    <t>Suit2</t>
+  </si>
+  <si>
+    <t>Suit3</t>
+  </si>
+  <si>
+    <t>Clothing buy 10</t>
+  </si>
+  <si>
+    <t>Top1</t>
+  </si>
+  <si>
+    <t>Top2</t>
+  </si>
+  <si>
+    <t>Clothing buy 5</t>
+  </si>
+  <si>
+    <t>Top3</t>
+  </si>
+  <si>
+    <t>Bottom1</t>
+  </si>
+  <si>
+    <t>Clothing buy 4</t>
+  </si>
+  <si>
+    <t>Bottom2</t>
+  </si>
+  <si>
+    <t>Bottom3</t>
+  </si>
+  <si>
+    <t>Clothing buy 12</t>
+  </si>
+  <si>
+    <t>Gloves1</t>
+  </si>
+  <si>
+    <t>Gloves2</t>
+  </si>
+  <si>
+    <t>Gloves3</t>
+  </si>
+  <si>
+    <t>Armor1</t>
+  </si>
+  <si>
+    <t>Clothing buy 1</t>
+  </si>
+  <si>
+    <t>Armor2</t>
+  </si>
+  <si>
+    <t>Armor3</t>
+  </si>
+  <si>
+    <t>Leather1</t>
+  </si>
+  <si>
+    <t>Leather2</t>
+  </si>
+  <si>
+    <t>Leather3</t>
+  </si>
+  <si>
+    <t>Bed1</t>
+  </si>
+  <si>
+    <t>Furniture buy 2</t>
+  </si>
+  <si>
+    <t>Bed2</t>
+  </si>
+  <si>
+    <t>Furniture Delivery</t>
+  </si>
+  <si>
+    <t>Bed3</t>
+  </si>
+  <si>
+    <t>Furniture buy 6</t>
+  </si>
+  <si>
+    <t>Chair1</t>
+  </si>
+  <si>
+    <t>Chair2</t>
+  </si>
+  <si>
+    <t>Furniture buy 5</t>
+  </si>
+  <si>
+    <t>Chair3</t>
+  </si>
+  <si>
+    <t>Table1</t>
+  </si>
+  <si>
+    <t>Furniture buy 1</t>
+  </si>
+  <si>
+    <t>Table2</t>
+  </si>
+  <si>
+    <t>Table3</t>
+  </si>
+  <si>
+    <t>Furniture buy 7</t>
+  </si>
+  <si>
+    <t>Closet1</t>
+  </si>
+  <si>
+    <t>Closet2</t>
+  </si>
+  <si>
+    <t>Furniture buy 3</t>
+  </si>
+  <si>
+    <t>Closet3</t>
+  </si>
+  <si>
+    <t>FarmingTool1</t>
+  </si>
+  <si>
+    <t>FarmingTool2</t>
+  </si>
+  <si>
+    <t>FarmingTool3</t>
+  </si>
+  <si>
+    <t>Furniture buy 10</t>
+  </si>
+  <si>
+    <t>PearlPreciounMetals1</t>
+  </si>
+  <si>
+    <t>Jewelry Delivery</t>
+  </si>
+  <si>
+    <t>PearlPrecoiusMetals2</t>
+  </si>
+  <si>
+    <t>Jewelry buy 9</t>
+  </si>
+  <si>
+    <t>PearlPreciousMetals3</t>
+  </si>
+  <si>
+    <t>AnUnprocessedPearl1</t>
+  </si>
+  <si>
+    <t>Jewelry buy 6</t>
+  </si>
+  <si>
+    <t>AnUnprocessedPearl2</t>
+  </si>
+  <si>
+    <t>AnUnprocessedPearl3</t>
+  </si>
+  <si>
+    <t>Jewelry buy 18</t>
+  </si>
+  <si>
+    <t>PreciousMetals1</t>
+  </si>
+  <si>
+    <t>PreciousMetals2</t>
+  </si>
+  <si>
+    <t>Jewelry buy 10</t>
+  </si>
+  <si>
+    <t>PreciousMetals3</t>
+  </si>
+  <si>
+    <t>Bracelet1</t>
+  </si>
+  <si>
+    <t>Jewelry buy 3</t>
+  </si>
+  <si>
+    <t>Jewelry buy 16</t>
+  </si>
+  <si>
+    <t>Jewelry buy 11</t>
+  </si>
+  <si>
+    <t>Jewelry buy 14</t>
+  </si>
+  <si>
+    <t>Bracelet2</t>
+  </si>
+  <si>
+    <t>Beacelet3</t>
+  </si>
+  <si>
+    <t>Ring1</t>
+  </si>
+  <si>
+    <t>Ring2</t>
+  </si>
+  <si>
+    <t>Ring3</t>
+  </si>
+  <si>
+    <t>Neckace1</t>
+  </si>
+  <si>
+    <t>Necklace2</t>
+  </si>
+  <si>
+    <t>Necklace3</t>
+  </si>
+  <si>
+    <t>밀</t>
+  </si>
+  <si>
+    <t>보리</t>
+  </si>
+  <si>
+    <t>귀리</t>
+  </si>
+  <si>
+    <t>물고기</t>
+  </si>
+  <si>
+    <t>고기</t>
+  </si>
+  <si>
+    <t>사과</t>
+  </si>
+  <si>
+    <t>포도</t>
+  </si>
+  <si>
+    <t>빵</t>
+  </si>
+  <si>
+    <t>훈제물고기</t>
+  </si>
+  <si>
+    <t>훈제고기</t>
+  </si>
+  <si>
+    <t>사과와인</t>
+  </si>
+  <si>
+    <t>포도와인</t>
+  </si>
+  <si>
+    <t>과일잼</t>
+  </si>
+  <si>
+    <t>드레스</t>
+  </si>
+  <si>
+    <t>정장</t>
+  </si>
+  <si>
+    <t>상의</t>
+  </si>
+  <si>
+    <t>바지</t>
+  </si>
+  <si>
+    <t>장갑</t>
+  </si>
+  <si>
+    <t>갑옷</t>
+  </si>
+  <si>
+    <t>가죽</t>
+  </si>
+  <si>
+    <t>침대</t>
+  </si>
+  <si>
+    <t>의자</t>
+  </si>
+  <si>
+    <t>책상</t>
+  </si>
+  <si>
+    <t>옷장</t>
+  </si>
+  <si>
+    <t>농기구</t>
+  </si>
+  <si>
+    <t>진주목걸이</t>
+  </si>
+  <si>
+    <t>미가공진주</t>
+  </si>
+  <si>
+    <t>보석이 박힌 반지</t>
+  </si>
+  <si>
+    <t>팔찌</t>
+  </si>
+  <si>
+    <t>반지</t>
+  </si>
+  <si>
+    <t>목걸이</t>
+  </si>
+  <si>
+    <t>food</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스모키안 마을에서 비가공식품을 15kg치 사라!</t>
+    <t>pFood</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>골드벤 마을에서 비가공식품을 30kg치 팔아라!</t>
+    <t>furniture</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스모키안 마을에서 비가공식품을 50kg치 팔아라!</t>
+    <t>accesory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>골드벤 마을에서 비가공식품을 30kg치 사라!</t>
+    <t>sort</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>물건을 구매하자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물건을 판매하자</t>
+    <t>clothes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -164,9 +658,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65CF359-1C7B-43EC-B835-5BFB63C787A2}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.875" bestFit="1" customWidth="1"/>
@@ -514,33 +1011,33 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -548,116 +1045,2976 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>15</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="1">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="1">
+        <v>35</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>11</v>
+      <c r="H3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="1">
+        <v>50</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>50</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" t="s">
-        <v>11</v>
+      <c r="H4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" s="1">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="1">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="1">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="1">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" s="1">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="1">
+        <v>40</v>
+      </c>
+      <c r="F13" s="1">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="1">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="1">
+        <v>25</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="1">
+        <v>35</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="1">
+        <v>20</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" s="1">
+        <v>25</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" s="1">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5">
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" s="1">
+        <v>13</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="1">
+        <v>23</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" s="1">
+        <v>33</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="1">
+        <v>20</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" s="1">
+        <v>35</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E25" s="1">
+        <v>50</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E26" s="1">
         <v>30</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E27" s="1">
+        <v>40</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" s="1">
+        <v>50</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" s="1">
+        <v>28</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E30" s="1">
+        <v>33</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="1">
+        <v>38</v>
+      </c>
+      <c r="F31" s="1">
+        <v>3</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" s="1">
+        <v>13</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E33" s="1">
+        <v>19</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E34" s="1">
+        <v>25</v>
+      </c>
+      <c r="F34" s="1">
+        <v>3</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E35" s="1">
         <v>11</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E36" s="1">
+        <v>18</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E37" s="1">
+        <v>25</v>
+      </c>
+      <c r="F37" s="1">
+        <v>3</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" s="1">
+        <v>12</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" s="1">
+        <v>21</v>
+      </c>
+      <c r="F39" s="1">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" s="1">
+        <v>30</v>
+      </c>
+      <c r="F40" s="1">
+        <v>3</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1">
+        <v>3</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H44" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1">
+        <v>2</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H45" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3</v>
+      </c>
+      <c r="F48" s="1">
+        <v>2</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H48" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E49" s="1">
+        <v>5</v>
+      </c>
+      <c r="F49" s="1">
+        <v>3</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H50" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3</v>
+      </c>
+      <c r="F51" s="1">
+        <v>2</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H51" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E52" s="1">
+        <v>5</v>
+      </c>
+      <c r="F52" s="1">
+        <v>3</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H52" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E53" s="1">
+        <v>3</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H53" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" s="1">
+        <v>5</v>
+      </c>
+      <c r="F54" s="1">
+        <v>2</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H54" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55" s="1">
+        <v>7</v>
+      </c>
+      <c r="F55" s="1">
+        <v>3</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H55" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H56" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+      <c r="F57" s="1">
+        <v>2</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H57" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E58" s="1">
+        <v>3</v>
+      </c>
+      <c r="F58" s="1">
+        <v>3</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H58" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E59" s="1">
+        <v>2</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H59" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E60" s="1">
+        <v>5</v>
+      </c>
+      <c r="F60" s="1">
+        <v>2</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E61" s="1">
+        <v>7</v>
+      </c>
+      <c r="F61" s="1">
+        <v>3</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H62" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2</v>
+      </c>
+      <c r="F63" s="1">
+        <v>2</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H63" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" s="1">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1">
+        <v>3</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H64" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+      <c r="F65" s="1">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E66" s="1">
+        <v>4</v>
+      </c>
+      <c r="F66" s="1">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H66" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E67" s="1">
+        <v>6</v>
+      </c>
+      <c r="F67" s="1">
+        <v>3</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H67" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H68" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E69" s="1">
+        <v>3</v>
+      </c>
+      <c r="F69" s="1">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H69" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E70" s="1">
+        <v>5</v>
+      </c>
+      <c r="F70" s="1">
+        <v>3</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E71" s="1">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H71" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2</v>
+      </c>
+      <c r="F72" s="1">
+        <v>2</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H72" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" s="1">
+        <v>3</v>
+      </c>
+      <c r="F73" s="1">
+        <v>3</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H73" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E74" s="1">
+        <v>2</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H74" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E75" s="1">
+        <v>5</v>
+      </c>
+      <c r="F75" s="1">
+        <v>2</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H75" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E76" s="1">
+        <v>8</v>
+      </c>
+      <c r="F76" s="1">
+        <v>3</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H76" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E77" s="1">
+        <v>1</v>
+      </c>
+      <c r="F77" s="1">
+        <v>1</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H77" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E78" s="1">
+        <v>2</v>
+      </c>
+      <c r="F78" s="1">
+        <v>2</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H78" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3</v>
+      </c>
+      <c r="F79" s="1">
+        <v>3</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H79" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H80" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E81" s="1">
+        <v>2</v>
+      </c>
+      <c r="F81" s="1">
+        <v>2</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H81" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E82" s="1">
+        <v>3</v>
+      </c>
+      <c r="F82" s="1">
+        <v>3</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H82" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1">
+        <v>1</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H83" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E84" s="1">
+        <v>2</v>
+      </c>
+      <c r="F84" s="1">
+        <v>2</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H84" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E85" s="1">
+        <v>3</v>
+      </c>
+      <c r="F85" s="1">
+        <v>3</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H85" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="1">
+        <v>1</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H86" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E87" s="1">
+        <v>2</v>
+      </c>
+      <c r="F87" s="1">
+        <v>2</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H87" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E88" s="1">
+        <v>3</v>
+      </c>
+      <c r="F88" s="1">
+        <v>3</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H88" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H89" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E90" s="1">
+        <v>2</v>
+      </c>
+      <c r="F90" s="1">
+        <v>2</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H90" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E91" s="1">
+        <v>3</v>
+      </c>
+      <c r="F91" s="1">
+        <v>3</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H91" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H92" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E93" s="1">
+        <v>2</v>
+      </c>
+      <c r="F93" s="1">
+        <v>2</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H93" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E94" s="1">
+        <v>3</v>
+      </c>
+      <c r="F94" s="1">
+        <v>3</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H94" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Scripts/HH/Quest/QuestTable.xlsx
+++ b/Assets/Scripts/HH/Quest/QuestTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rlagh\OneDrive\문서\GitHub\HaveToTrade2\Assets\Scripts\HH\Quest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145B48A2-CCF2-455E-B8DB-29D53CFBB301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEC4941-A7D5-4AB3-B8B2-1474A9B56B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D7B09D39-F076-47B8-9C94-38323AFFEA98}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{D7B09D39-F076-47B8-9C94-38323AFFEA98}"/>
   </bookViews>
   <sheets>
     <sheet name="quest" sheetId="1" r:id="rId1"/>
@@ -1003,10 +1003,14 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
